--- a/emc/dist/20261025_台光電模型_v0.2.1.xlsx
+++ b/emc/dist/20261025_台光電模型_v0.2.1.xlsx
@@ -7108,7 +7108,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7345,7 +7345,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7466,7 +7466,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7587,7 +7587,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7708,7 +7708,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7829,7 +7829,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/emc/dist/20261025_台光電模型_v0.2.1.xlsx
+++ b/emc/dist/20261025_台光電模型_v0.2.1.xlsx
@@ -5927,7 +5927,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -5946,7 +5946,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/emc/dist/20261025_台光電模型_v0.2.1.xlsx
+++ b/emc/dist/20261025_台光電模型_v0.2.1.xlsx
@@ -6240,7 +6240,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -6259,7 +6259,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6804,7 +6804,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -6823,7 +6823,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -43393,7 +43393,7 @@
         <v>34</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>35</v>
@@ -46640,7 +46640,7 @@
       </c>
       <c r="C10" s="18" t="n">
         <f aca="false">PL!D70*PL!D72</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="D10" s="18" t="n">
         <f aca="false">PL!E70*PL!E72</f>
@@ -46698,7 +46698,7 @@
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">PL!E76/fx</f>
-        <v>9.58582785691217</v>
+        <v>9.58582785691218</v>
       </c>
       <c r="E12" s="19" t="n">
         <f aca="false">PL!F76/fx</f>
@@ -46847,7 +46847,7 @@
       </c>
       <c r="C18" s="18" t="n">
         <f aca="false">PL!D70*PL!D72-PL!D83/fx</f>
-        <v>4.42819508034737</v>
+        <v>4.42819508034736</v>
       </c>
       <c r="D18" s="18" t="n">
         <f aca="false">PL!E70*PL!E72-PL!E83/fx</f>
@@ -47227,11 +47227,11 @@
       </c>
       <c r="F17" s="18" t="n">
         <f aca="false">F132</f>
-        <v>427.779457298675</v>
+        <v>427.779457298676</v>
       </c>
       <c r="G17" s="18" t="n">
         <f aca="false">G132</f>
-        <v>496.115732482044</v>
+        <v>496.115732482045</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47251,11 +47251,11 @@
       </c>
       <c r="F18" s="13" t="n">
         <f aca="false">F133</f>
-        <v>0.285960786719756</v>
+        <v>0.285960786719757</v>
       </c>
       <c r="G18" s="13" t="n">
         <f aca="false">G133</f>
-        <v>0.159746509603094</v>
+        <v>0.159746509603093</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47279,11 +47279,11 @@
       </c>
       <c r="F19" s="18" t="n">
         <f aca="false">F130</f>
-        <v>330.022104409475</v>
+        <v>330.022104409476</v>
       </c>
       <c r="G19" s="18" t="n">
         <f aca="false">G130</f>
-        <v>393.470511948384</v>
+        <v>393.470511948385</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47331,11 +47331,11 @@
       </c>
       <c r="F21" s="13" t="n">
         <f aca="false">F135</f>
-        <v>0.891789727267514</v>
+        <v>0.891789727267515</v>
       </c>
       <c r="G21" s="13" t="n">
         <f aca="false">G135</f>
-        <v>0.878832925015579</v>
+        <v>0.87883292501558</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47415,7 +47415,7 @@
       </c>
       <c r="F24" s="18" t="n">
         <f aca="false">F147</f>
-        <v>94.4923061633998</v>
+        <v>94.4923061633999</v>
       </c>
       <c r="G24" s="18" t="n">
         <f aca="false">G147</f>
@@ -47447,7 +47447,7 @@
       </c>
       <c r="G25" s="14" t="n">
         <f aca="false">G150</f>
-        <v>286.612100014017</v>
+        <v>286.612100014018</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47467,7 +47467,7 @@
       </c>
       <c r="F26" s="13" t="n">
         <f aca="false">F151</f>
-        <v>0.25833734464472</v>
+        <v>0.258337344644721</v>
       </c>
       <c r="G26" s="13" t="n">
         <f aca="false">G151</f>
@@ -47500,7 +47500,7 @@
       </c>
       <c r="F29" s="18" t="n">
         <f aca="false">F179</f>
-        <v>345.273931196306</v>
+        <v>345.273931196307</v>
       </c>
       <c r="G29" s="18" t="n">
         <f aca="false">G179</f>
@@ -47524,7 +47524,7 @@
       </c>
       <c r="F30" s="13" t="n">
         <f aca="false">F180</f>
-        <v>0.037938425091363</v>
+        <v>0.0379384250913639</v>
       </c>
       <c r="G30" s="13" t="n">
         <f aca="false">G180</f>
@@ -47552,7 +47552,7 @@
       </c>
       <c r="F31" s="18" t="n">
         <f aca="false">F177</f>
-        <v>247.516578307106</v>
+        <v>247.516578307107</v>
       </c>
       <c r="G31" s="18" t="n">
         <f aca="false">G177</f>
@@ -47604,11 +47604,11 @@
       </c>
       <c r="F33" s="13" t="n">
         <f aca="false">F182</f>
-        <v>0.719790863447547</v>
+        <v>0.719790863447548</v>
       </c>
       <c r="G33" s="13" t="n">
         <f aca="false">G182</f>
-        <v>0.673831635359789</v>
+        <v>0.67383163535979</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47688,11 +47688,11 @@
       </c>
       <c r="F36" s="18" t="n">
         <f aca="false">F194</f>
-        <v>74.322027053004</v>
+        <v>74.3220270530041</v>
       </c>
       <c r="G36" s="18" t="n">
         <f aca="false">G194</f>
-        <v>76.7330667025937</v>
+        <v>76.7330667025938</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47716,7 +47716,7 @@
       </c>
       <c r="F37" s="14" t="n">
         <f aca="false">F197</f>
-        <v>207.43530327158</v>
+        <v>207.435303271581</v>
       </c>
       <c r="G37" s="14" t="n">
         <f aca="false">G197</f>
@@ -47740,11 +47740,11 @@
       </c>
       <c r="F38" s="13" t="n">
         <f aca="false">F198</f>
-        <v>-0.0102666982350085</v>
+        <v>-0.0102666982350073</v>
       </c>
       <c r="G38" s="13" t="n">
         <f aca="false">G198</f>
-        <v>0.0324404452514486</v>
+        <v>0.0324404452514484</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47833,7 +47833,7 @@
       </c>
       <c r="D63" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E63" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -48001,7 +48001,7 @@
       </c>
       <c r="D70" s="19" t="n">
         <f aca="false">D65*D69/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E70" s="19" t="n">
         <f aca="false">E65*E69/1000</f>
@@ -48140,7 +48140,7 @@
       </c>
       <c r="E76" s="18" t="n">
         <f aca="false">E71*E75*E72</f>
-        <v>306.746491421189</v>
+        <v>306.74649142119</v>
       </c>
       <c r="F76" s="18" t="n">
         <f aca="false">F71*F75*F72</f>
@@ -48869,7 +48869,7 @@
       </c>
       <c r="D110" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E110" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -49037,7 +49037,7 @@
       </c>
       <c r="D117" s="19" t="n">
         <f aca="false">D112*D116/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E117" s="19" t="n">
         <f aca="false">E112*E116/1000</f>
@@ -49176,15 +49176,15 @@
       </c>
       <c r="E123" s="18" t="n">
         <f aca="false">E118*E122*E119</f>
-        <v>306.746491421189</v>
+        <v>306.74649142119</v>
       </c>
       <c r="F123" s="18" t="n">
         <f aca="false">F118*F122*F119</f>
-        <v>330.022104409475</v>
+        <v>330.022104409476</v>
       </c>
       <c r="G123" s="18" t="n">
         <f aca="false">G118*G122*G119</f>
-        <v>393.470511948384</v>
+        <v>393.470511948385</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49328,11 +49328,11 @@
       </c>
       <c r="F130" s="18" t="n">
         <f aca="false">MIN(F123,F128-F129)</f>
-        <v>330.022104409475</v>
+        <v>330.022104409476</v>
       </c>
       <c r="G130" s="18" t="n">
         <f aca="false">MIN(G123,G128-G129)</f>
-        <v>393.470511948384</v>
+        <v>393.470511948385</v>
       </c>
       <c r="H130" s="3" t="s">
         <v>492</v>
@@ -49376,11 +49376,11 @@
       </c>
       <c r="F132" s="18" t="n">
         <f aca="false">F130+F129</f>
-        <v>427.779457298675</v>
+        <v>427.779457298676</v>
       </c>
       <c r="G132" s="18" t="n">
         <f aca="false">G130+G129</f>
-        <v>496.115732482044</v>
+        <v>496.115732482045</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49400,11 +49400,11 @@
       </c>
       <c r="F133" s="13" t="n">
         <f aca="false">F132/E132-1</f>
-        <v>0.285960786719756</v>
+        <v>0.285960786719757</v>
       </c>
       <c r="G133" s="13" t="n">
         <f aca="false">G132/F132-1</f>
-        <v>0.159746509603094</v>
+        <v>0.159746509603093</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49452,11 +49452,11 @@
       </c>
       <c r="F135" s="13" t="n">
         <f aca="false">(F123+F129)/F128</f>
-        <v>0.891789727267514</v>
+        <v>0.891789727267515</v>
       </c>
       <c r="G135" s="13" t="n">
         <f aca="false">(G123+G129)/G128</f>
-        <v>0.878832925015579</v>
+        <v>0.87883292501558</v>
       </c>
       <c r="H135" s="3" t="s">
         <v>497</v>
@@ -49554,7 +49554,7 @@
       </c>
       <c r="F140" s="18" t="n">
         <f aca="false">F130*F139+F129*$D$138</f>
-        <v>144.712687903442</v>
+        <v>144.712687903443</v>
       </c>
       <c r="G140" s="18" t="n">
         <f aca="false">G130*G139+G129*$D$138</f>
@@ -49745,7 +49745,7 @@
       </c>
       <c r="F147" s="18" t="n">
         <f aca="false">(F144+F146)*nir_f</f>
-        <v>94.4923061633998</v>
+        <v>94.4923061633999</v>
       </c>
       <c r="G147" s="18" t="n">
         <f aca="false">(G144+G146)*nir_f</f>
@@ -49833,7 +49833,7 @@
       </c>
       <c r="G150" s="19" t="n">
         <f aca="false">G147/G149</f>
-        <v>286.612100014017</v>
+        <v>286.612100014018</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49853,7 +49853,7 @@
       </c>
       <c r="F151" s="13" t="n">
         <f aca="false">F150/E150-1</f>
-        <v>0.25833734464472</v>
+        <v>0.258337344644721</v>
       </c>
       <c r="G151" s="13" t="n">
         <f aca="false">G150/F150-1</f>
@@ -49905,7 +49905,7 @@
       </c>
       <c r="D157" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E157" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -50073,7 +50073,7 @@
       </c>
       <c r="D164" s="19" t="n">
         <f aca="false">D159*D163/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E164" s="19" t="n">
         <f aca="false">E159*E163/1000</f>
@@ -50212,11 +50212,11 @@
       </c>
       <c r="E170" s="18" t="n">
         <f aca="false">E165*E169*E166</f>
-        <v>306.746491421189</v>
+        <v>306.74649142119</v>
       </c>
       <c r="F170" s="18" t="n">
         <f aca="false">F165*F169*F166</f>
-        <v>247.516578307106</v>
+        <v>247.516578307107</v>
       </c>
       <c r="G170" s="18" t="n">
         <f aca="false">G165*G169*G166</f>
@@ -50364,7 +50364,7 @@
       </c>
       <c r="F177" s="18" t="n">
         <f aca="false">MIN(F170,F175-F176)</f>
-        <v>247.516578307106</v>
+        <v>247.516578307107</v>
       </c>
       <c r="G177" s="18" t="n">
         <f aca="false">MIN(G170,G175-G176)</f>
@@ -50412,7 +50412,7 @@
       </c>
       <c r="F179" s="18" t="n">
         <f aca="false">F177+F176</f>
-        <v>345.273931196306</v>
+        <v>345.273931196307</v>
       </c>
       <c r="G179" s="18" t="n">
         <f aca="false">G177+G176</f>
@@ -50436,7 +50436,7 @@
       </c>
       <c r="F180" s="13" t="n">
         <f aca="false">F179/E179-1</f>
-        <v>0.037938425091363</v>
+        <v>0.0379384250913639</v>
       </c>
       <c r="G180" s="13" t="n">
         <f aca="false">G179/F179-1</f>
@@ -50488,11 +50488,11 @@
       </c>
       <c r="F182" s="13" t="n">
         <f aca="false">(F170+F176)/F175</f>
-        <v>0.719790863447547</v>
+        <v>0.719790863447548</v>
       </c>
       <c r="G182" s="13" t="n">
         <f aca="false">(G170+G176)/G175</f>
-        <v>0.673831635359789</v>
+        <v>0.67383163535979</v>
       </c>
       <c r="H182" s="3" t="s">
         <v>497</v>
@@ -50519,7 +50519,7 @@
       </c>
       <c r="G183" s="17" t="n">
         <f aca="false">G177/fx/G159*1000</f>
-        <v>240.54150966217</v>
+        <v>240.541509662171</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50702,11 +50702,11 @@
       </c>
       <c r="F191" s="18" t="n">
         <f aca="false">F187-F190</f>
-        <v>96.0221130558494</v>
+        <v>96.0221130558495</v>
       </c>
       <c r="G191" s="18" t="n">
         <f aca="false">G187-G190</f>
-        <v>99.1533333799918</v>
+        <v>99.1533333799919</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50781,11 +50781,11 @@
       </c>
       <c r="F194" s="18" t="n">
         <f aca="false">(F191+F193)*nir_f</f>
-        <v>74.322027053004</v>
+        <v>74.3220270530041</v>
       </c>
       <c r="G194" s="18" t="n">
         <f aca="false">(G191+G193)*nir_f</f>
-        <v>76.7330667025937</v>
+        <v>76.7330667025938</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50865,7 +50865,7 @@
       </c>
       <c r="F197" s="19" t="n">
         <f aca="false">F194/F196</f>
-        <v>207.43530327158</v>
+        <v>207.435303271581</v>
       </c>
       <c r="G197" s="19" t="n">
         <f aca="false">G194/G196</f>
@@ -50889,11 +50889,11 @@
       </c>
       <c r="F198" s="13" t="n">
         <f aca="false">F197/E197-1</f>
-        <v>-0.0102666982350085</v>
+        <v>-0.0102666982350073</v>
       </c>
       <c r="G198" s="13" t="n">
         <f aca="false">G197/F197-1</f>
-        <v>0.0324404452514486</v>
+        <v>0.0324404452514484</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51312,15 +51312,15 @@
       </c>
       <c r="F216" s="18" t="n">
         <f aca="false">F132</f>
-        <v>427.779457298675</v>
+        <v>427.779457298676</v>
       </c>
       <c r="G216" s="18" t="n">
         <f aca="false">G132</f>
-        <v>496.115732482044</v>
+        <v>496.115732482045</v>
       </c>
       <c r="H216" s="21" t="n">
         <f aca="false">G216*(1+H217)</f>
-        <v>555.565779997264</v>
+        <v>555.565779997265</v>
       </c>
       <c r="I216" s="21" t="n">
         <f aca="false">H216*(1+I217)</f>
@@ -51352,11 +51352,11 @@
       </c>
       <c r="F217" s="13" t="n">
         <f aca="false">F216/E216-1</f>
-        <v>0.285960786719756</v>
+        <v>0.285960786719757</v>
       </c>
       <c r="G217" s="13" t="n">
         <f aca="false">G216/F216-1</f>
-        <v>0.159746509603094</v>
+        <v>0.159746509603093</v>
       </c>
       <c r="H217" s="22" t="n">
         <f aca="false">$G$217+($C$223-$G$217)*1/3</f>
@@ -51392,7 +51392,7 @@
       </c>
       <c r="F218" s="18" t="n">
         <f aca="false">F147</f>
-        <v>94.4923061633998</v>
+        <v>94.4923061633999</v>
       </c>
       <c r="G218" s="18" t="n">
         <f aca="false">G147</f>
@@ -51519,7 +51519,7 @@
       </c>
       <c r="G221" s="14" t="n">
         <f aca="false">G150</f>
-        <v>286.612100014017</v>
+        <v>286.612100014018</v>
       </c>
       <c r="H221" s="24" t="n">
         <f aca="false">H218/H220</f>
@@ -51527,7 +51527,7 @@
       </c>
       <c r="I221" s="24" t="n">
         <f aca="false">I218/I220</f>
-        <v>323.499461477938</v>
+        <v>323.499461477939</v>
       </c>
       <c r="J221" s="24" t="n">
         <f aca="false">J218/J220</f>
@@ -51552,7 +51552,7 @@
       </c>
       <c r="F222" s="13" t="n">
         <f aca="false">F221/E221-1</f>
-        <v>0.25833734464472</v>
+        <v>0.258337344644721</v>
       </c>
       <c r="G222" s="13" t="n">
         <f aca="false">G221/F221-1</f>
@@ -51564,7 +51564,7 @@
       </c>
       <c r="I222" s="22" t="n">
         <f aca="false">I221/H221-1</f>
-        <v>0.0426770375734098</v>
+        <v>0.0426770375734096</v>
       </c>
       <c r="J222" s="22" t="n">
         <f aca="false">J221/I221-1</f>
@@ -51662,7 +51662,7 @@
       </c>
       <c r="F228" s="18" t="n">
         <f aca="false">F179</f>
-        <v>345.273931196306</v>
+        <v>345.273931196307</v>
       </c>
       <c r="G228" s="18" t="n">
         <f aca="false">G179</f>
@@ -51670,7 +51670,7 @@
       </c>
       <c r="H228" s="21" t="n">
         <f aca="false">G228*(1+H229)</f>
-        <v>408.716023711882</v>
+        <v>408.716023711883</v>
       </c>
       <c r="I228" s="21" t="n">
         <f aca="false">H228*(1+I229)</f>
@@ -51702,7 +51702,7 @@
       </c>
       <c r="F229" s="13" t="n">
         <f aca="false">F228/E228-1</f>
-        <v>0.037938425091363</v>
+        <v>0.0379384250913639</v>
       </c>
       <c r="G229" s="13" t="n">
         <f aca="false">G228/F228-1</f>
@@ -51710,7 +51710,7 @@
       </c>
       <c r="H229" s="22" t="n">
         <f aca="false">$G$229+($C$235-$G$229)*1/3</f>
-        <v>0.0744682525027421</v>
+        <v>0.0744682525027423</v>
       </c>
       <c r="I229" s="22" t="n">
         <f aca="false">$G$229+($C$235-$G$229)*2/3</f>
@@ -51742,23 +51742,23 @@
       </c>
       <c r="F230" s="18" t="n">
         <f aca="false">F194</f>
-        <v>74.322027053004</v>
+        <v>74.3220270530041</v>
       </c>
       <c r="G230" s="18" t="n">
         <f aca="false">G194</f>
-        <v>76.7330667025937</v>
+        <v>76.7330667025938</v>
       </c>
       <c r="H230" s="21" t="n">
         <f aca="false">H228*H231</f>
-        <v>76.950761149838</v>
+        <v>76.9507611498381</v>
       </c>
       <c r="I230" s="21" t="n">
         <f aca="false">I228*I231</f>
-        <v>74.8293586087623</v>
+        <v>74.8293586087624</v>
       </c>
       <c r="J230" s="21" t="n">
         <f aca="false">J228*J231</f>
-        <v>70.4547191824039</v>
+        <v>70.454719182404</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51865,7 +51865,7 @@
       </c>
       <c r="F233" s="14" t="n">
         <f aca="false">F197</f>
-        <v>207.43530327158</v>
+        <v>207.435303271581</v>
       </c>
       <c r="G233" s="14" t="n">
         <f aca="false">G197</f>
@@ -51902,23 +51902,23 @@
       </c>
       <c r="F234" s="13" t="n">
         <f aca="false">F233/E233-1</f>
-        <v>-0.0102666982350085</v>
+        <v>-0.0102666982350073</v>
       </c>
       <c r="G234" s="13" t="n">
         <f aca="false">G233/F233-1</f>
-        <v>0.0324404452514486</v>
+        <v>0.0324404452514484</v>
       </c>
       <c r="H234" s="22" t="n">
         <f aca="false">H233/G233-1</f>
-        <v>0.00283703566922577</v>
+        <v>0.00283703566922622</v>
       </c>
       <c r="I234" s="22" t="n">
         <f aca="false">I233/H233-1</f>
-        <v>-0.0275683113380123</v>
+        <v>-0.0275683113380124</v>
       </c>
       <c r="J234" s="22" t="n">
         <f aca="false">J233/I233-1</f>
-        <v>-0.0584615384615386</v>
+        <v>-0.0584615384615385</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52085,7 +52085,7 @@
       </c>
       <c r="C10" s="16" t="n">
         <f aca="false">px/PL!G25</f>
-        <v>17.689413670086</v>
+        <v>17.6894136700859</v>
       </c>
       <c r="D10" s="16" t="n">
         <f aca="false">px/PL!G37</f>
@@ -52384,7 +52384,7 @@
       </c>
       <c r="C29" s="16" t="n">
         <f aca="false">px*A29/PL!F37</f>
-        <v>18.3310166593083</v>
+        <v>18.3310166593082</v>
       </c>
       <c r="D29" s="16" t="n">
         <f aca="false">pe_mid</f>
@@ -52426,7 +52426,7 @@
       </c>
       <c r="C31" s="16" t="n">
         <f aca="false">px*A31/PL!F37</f>
-        <v>29.5740402103507</v>
+        <v>29.5740402103506</v>
       </c>
       <c r="D31" s="16" t="n">
         <f aca="false">pe_mid</f>
@@ -53031,7 +53031,7 @@
       </c>
       <c r="D90" s="14" t="n">
         <f aca="false">PL!F233</f>
-        <v>207.43530327158</v>
+        <v>207.435303271581</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53044,7 +53044,7 @@
       </c>
       <c r="C91" s="14" t="n">
         <f aca="false">PL!G221</f>
-        <v>286.612100014017</v>
+        <v>286.612100014018</v>
       </c>
       <c r="D91" s="14" t="n">
         <f aca="false">PL!G233</f>
@@ -53078,7 +53078,7 @@
       </c>
       <c r="C93" s="14" t="n">
         <f aca="false">PL!I221</f>
-        <v>323.499461477938</v>
+        <v>323.499461477939</v>
       </c>
       <c r="D93" s="14" t="n">
         <f aca="false">PL!I233</f>
@@ -53146,7 +53146,7 @@
       </c>
       <c r="C98" s="14" t="n">
         <f aca="false">C90*(1-$B$96)</f>
-        <v>227.607794604717</v>
+        <v>227.607794604718</v>
       </c>
       <c r="D98" s="14" t="n">
         <f aca="false">D90*(1-$B$96)</f>
@@ -53251,11 +53251,11 @@
       </c>
       <c r="C104" s="17" t="n">
         <f aca="false">C103*(1+tp_r)</f>
-        <v>4171.3357449988</v>
+        <v>4171.33574499881</v>
       </c>
       <c r="D104" s="17" t="n">
         <f aca="false">D103*(1+tp_r)</f>
-        <v>2690.62334592878</v>
+        <v>2690.62334592879</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53415,7 +53415,7 @@
       </c>
       <c r="B118" s="27" t="n">
         <f aca="false">tp_w_dcf*B105+(1-tp_w_dcf)*B114</f>
-        <v>5477.38585591289</v>
+        <v>5477.3858559129</v>
       </c>
       <c r="E118" s="7" t="s">
         <v>671</v>
@@ -53451,7 +53451,7 @@
       </c>
       <c r="B121" s="13" t="n">
         <f aca="false">B118/px-1</f>
-        <v>0.080352239825028</v>
+        <v>0.0803522398250287</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>676</v>
@@ -53463,7 +53463,7 @@
       </c>
       <c r="B122" s="13" t="n">
         <f aca="false">B119/px-1</f>
-        <v>0.322031451561354</v>
+        <v>0.322031451561355</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53472,7 +53472,7 @@
       </c>
       <c r="B123" s="13" t="n">
         <f aca="false">B113/cons_feps-1</f>
-        <v>0.51005309139954</v>
+        <v>0.510053091399541</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>679</v>
@@ -54050,15 +54050,15 @@
       </c>
       <c r="E14" s="18" t="n">
         <f aca="false">PL!F132</f>
-        <v>427.779457298675</v>
+        <v>427.779457298676</v>
       </c>
       <c r="F14" s="13" t="n">
         <f aca="false">E14/B14-1</f>
-        <v>-0.167565868394848</v>
+        <v>-0.167565868394847</v>
       </c>
       <c r="G14" s="18" t="n">
         <f aca="false">PL!F179</f>
-        <v>345.273931196306</v>
+        <v>345.273931196307</v>
       </c>
       <c r="H14" s="13" t="n">
         <f aca="false">G14/B14-1</f>
@@ -54093,15 +54093,15 @@
       </c>
       <c r="F15" s="13" t="n">
         <f aca="false">E15/B15-1</f>
-        <v>-0.372068481577793</v>
+        <v>-0.372068481577792</v>
       </c>
       <c r="G15" s="19" t="n">
         <f aca="false">PL!F197</f>
-        <v>207.43530327158</v>
+        <v>207.435303271581</v>
       </c>
       <c r="H15" s="13" t="n">
         <f aca="false">G15/B15-1</f>
-        <v>-0.506106420781952</v>
+        <v>-0.506106420781951</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>40</v>
@@ -54129,7 +54129,7 @@
       </c>
       <c r="D17" s="13" t="n">
         <f aca="false">C17-B17</f>
-        <v>0.0733061657411386</v>
+        <v>0.0733061657411391</v>
       </c>
       <c r="E17" s="13" t="n">
         <f aca="false">PL!D120</f>
@@ -54137,7 +54137,7 @@
       </c>
       <c r="F17" s="13" t="n">
         <f aca="false">E17-B17</f>
-        <v>0.0733061657411386</v>
+        <v>0.0733061657411391</v>
       </c>
       <c r="G17" s="13" t="n">
         <f aca="false">PL!D167</f>
@@ -54145,7 +54145,7 @@
       </c>
       <c r="H17" s="13" t="n">
         <f aca="false">G17-B17</f>
-        <v>0.0733061657411386</v>
+        <v>0.0733061657411391</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>725</v>
@@ -54168,7 +54168,7 @@
       </c>
       <c r="D18" s="13" t="n">
         <f aca="false">C18-B18</f>
-        <v>-0.0406938342588614</v>
+        <v>-0.0406938342588609</v>
       </c>
       <c r="E18" s="13" t="n">
         <f aca="false">PL!D120</f>
@@ -54176,7 +54176,7 @@
       </c>
       <c r="F18" s="13" t="n">
         <f aca="false">E18-B18</f>
-        <v>-0.0406938342588614</v>
+        <v>-0.0406938342588609</v>
       </c>
       <c r="G18" s="13" t="n">
         <f aca="false">PL!D167</f>
@@ -54184,7 +54184,7 @@
       </c>
       <c r="H18" s="13" t="n">
         <f aca="false">G18-B18</f>
-        <v>-0.0406938342588614</v>
+        <v>-0.0406938342588609</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>728</v>
@@ -54353,11 +54353,11 @@
       </c>
       <c r="E25" s="13" t="n">
         <f aca="false">PL!F135</f>
-        <v>0.891789727267514</v>
+        <v>0.891789727267515</v>
       </c>
       <c r="G25" s="13" t="n">
         <f aca="false">PL!F182</f>
-        <v>0.719790863447547</v>
+        <v>0.719790863447548</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>112</v>
@@ -54503,7 +54503,7 @@
       </c>
       <c r="D34" s="13" t="n">
         <f aca="false">C34/B34-1</f>
-        <v>0.51005309139954</v>
+        <v>0.510053091399541</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>365</v>
@@ -54522,7 +54522,7 @@
       </c>
       <c r="C35" s="14" t="n">
         <f aca="false">Val!B118</f>
-        <v>5477.38585591289</v>
+        <v>5477.3858559129</v>
       </c>
       <c r="D35" s="13" t="n">
         <f aca="false">C35/B35-1</f>
@@ -54702,11 +54702,11 @@
       </c>
       <c r="H5" s="18" t="n">
         <f aca="false">F65</f>
-        <v>412.40281162935</v>
+        <v>412.402811629351</v>
       </c>
       <c r="I5" s="18" t="n">
         <f aca="false">F63</f>
-        <v>314.64545874015</v>
+        <v>314.645458740151</v>
       </c>
       <c r="J5" s="13" t="n">
         <f aca="false">F74</f>
@@ -54718,7 +54718,7 @@
       </c>
       <c r="L5" s="13" t="n">
         <f aca="false">K5/K$4-1</f>
-        <v>-0.153467391036592</v>
+        <v>-0.153467391036591</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54798,11 +54798,11 @@
       </c>
       <c r="H7" s="18" t="n">
         <f aca="false">F159</f>
-        <v>472.351408181564</v>
+        <v>472.351408181565</v>
       </c>
       <c r="I7" s="18" t="n">
         <f aca="false">F157</f>
-        <v>374.594055292364</v>
+        <v>374.594055292365</v>
       </c>
       <c r="J7" s="13" t="n">
         <f aca="false">F168</f>
@@ -54814,7 +54814,7 @@
       </c>
       <c r="L7" s="13" t="n">
         <f aca="false">K7/K$4-1</f>
-        <v>-0.0167305324105962</v>
+        <v>-0.0167305324105954</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54910,7 +54910,7 @@
       </c>
       <c r="L9" s="13" t="n">
         <f aca="false">K9/K$4-1</f>
-        <v>-0.0870302732861082</v>
+        <v>-0.0870302732861072</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55230,7 +55230,7 @@
       </c>
       <c r="H16" s="18" t="n">
         <f aca="false">F582</f>
-        <v>510.284983401044</v>
+        <v>510.284983401045</v>
       </c>
       <c r="I16" s="18" t="n">
         <f aca="false">F580</f>
@@ -55242,11 +55242,11 @@
       </c>
       <c r="K16" s="14" t="n">
         <f aca="false">F600</f>
-        <v>319.686817405118</v>
+        <v>319.686817405119</v>
       </c>
       <c r="L16" s="13" t="n">
         <f aca="false">K16/K$4-1</f>
-        <v>0.0686544818344392</v>
+        <v>0.0686544818344401</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55278,11 +55278,11 @@
       </c>
       <c r="H17" s="18" t="n">
         <f aca="false">F629</f>
-        <v>427.779457298675</v>
+        <v>427.779457298676</v>
       </c>
       <c r="I17" s="18" t="n">
         <f aca="false">F627</f>
-        <v>330.022104409475</v>
+        <v>330.022104409476</v>
       </c>
       <c r="J17" s="13" t="n">
         <f aca="false">F638</f>
@@ -55294,7 +55294,7 @@
       </c>
       <c r="L17" s="13" t="n">
         <f aca="false">K17/K$4-1</f>
-        <v>-0.118394773061336</v>
+        <v>-0.118394773061335</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55566,11 +55566,11 @@
       </c>
       <c r="H23" s="18" t="n">
         <f aca="false">PL!F132</f>
-        <v>427.779457298675</v>
+        <v>427.779457298676</v>
       </c>
       <c r="I23" s="18" t="n">
         <f aca="false">PL!F130</f>
-        <v>330.022104409475</v>
+        <v>330.022104409476</v>
       </c>
       <c r="J23" s="13" t="n">
         <f aca="false">PL!F141</f>
@@ -55582,7 +55582,7 @@
       </c>
       <c r="L23" s="13" t="n">
         <f aca="false">K23/K$4-1</f>
-        <v>-0.118394773061336</v>
+        <v>-0.118394773061335</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55614,11 +55614,11 @@
       </c>
       <c r="H24" s="18" t="n">
         <f aca="false">PL!F179</f>
-        <v>345.273931196306</v>
+        <v>345.273931196307</v>
       </c>
       <c r="I24" s="18" t="n">
         <f aca="false">PL!F177</f>
-        <v>247.516578307106</v>
+        <v>247.516578307107</v>
       </c>
       <c r="J24" s="13" t="n">
         <f aca="false">PL!F188</f>
@@ -55626,7 +55626,7 @@
       </c>
       <c r="K24" s="14" t="n">
         <f aca="false">PL!F197</f>
-        <v>207.43530327158</v>
+        <v>207.435303271581</v>
       </c>
       <c r="L24" s="13" t="n">
         <f aca="false">K24/K$4-1</f>
@@ -55683,7 +55683,7 @@
       </c>
       <c r="D43" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E43" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -55851,7 +55851,7 @@
       </c>
       <c r="D50" s="19" t="n">
         <f aca="false">D45*D49/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E50" s="19" t="n">
         <f aca="false">E45*E49/1000</f>
@@ -55990,11 +55990,11 @@
       </c>
       <c r="E56" s="18" t="n">
         <f aca="false">E51*E55*E52</f>
-        <v>245.687948105123</v>
+        <v>245.687948105124</v>
       </c>
       <c r="F56" s="18" t="n">
         <f aca="false">F51*F55*F52</f>
-        <v>314.64545874015</v>
+        <v>314.645458740151</v>
       </c>
       <c r="G56" s="18" t="n">
         <f aca="false">G51*G55*G52</f>
@@ -56142,7 +56142,7 @@
       </c>
       <c r="F63" s="18" t="n">
         <f aca="false">MIN(F56,F61-F62)</f>
-        <v>314.64545874015</v>
+        <v>314.645458740151</v>
       </c>
       <c r="G63" s="18" t="n">
         <f aca="false">MIN(G56,G61-G62)</f>
@@ -56190,11 +56190,11 @@
       </c>
       <c r="F65" s="18" t="n">
         <f aca="false">F63+F62</f>
-        <v>412.40281162935</v>
+        <v>412.402811629351</v>
       </c>
       <c r="G65" s="18" t="n">
         <f aca="false">G63+G62</f>
-        <v>430.348075323968</v>
+        <v>430.348075323969</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56214,11 +56214,11 @@
       </c>
       <c r="F66" s="13" t="n">
         <f aca="false">F65/E65-1</f>
-        <v>0.239736586317748</v>
+        <v>0.239736586317749</v>
       </c>
       <c r="G66" s="13" t="n">
         <f aca="false">G65/F65-1</f>
-        <v>0.0435139217982494</v>
+        <v>0.0435139217982496</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56246,7 +56246,7 @@
       </c>
       <c r="G67" s="13" t="n">
         <f aca="false">G63/G65</f>
-        <v>0.761483258740292</v>
+        <v>0.761483258740293</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56266,11 +56266,11 @@
       </c>
       <c r="F68" s="13" t="n">
         <f aca="false">(F56+F62)/F61</f>
-        <v>0.859734109790394</v>
+        <v>0.859734109790395</v>
       </c>
       <c r="G68" s="13" t="n">
         <f aca="false">(G56+G62)/G61</f>
-        <v>0.762330305309307</v>
+        <v>0.762330305309308</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>497</v>
@@ -56293,7 +56293,7 @@
       </c>
       <c r="F69" s="17" t="n">
         <f aca="false">F63/fx/F45*1000</f>
-        <v>186.25255431044</v>
+        <v>186.252554310441</v>
       </c>
       <c r="G69" s="17" t="n">
         <f aca="false">G63/fx/G45*1000</f>
@@ -56368,7 +56368,7 @@
       </c>
       <c r="F73" s="18" t="n">
         <f aca="false">F63*F72+F62*$D$71</f>
-        <v>139.298135934896</v>
+        <v>139.298135934897</v>
       </c>
       <c r="G73" s="18" t="n">
         <f aca="false">G63*G72+G62*$D$71</f>
@@ -56428,7 +56428,7 @@
       </c>
       <c r="G75" s="18" t="n">
         <f aca="false">F75*(1+MAX(0,phi*G66))</f>
-        <v>22.5362919803019</v>
+        <v>22.536291980302</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56456,7 +56456,7 @@
       </c>
       <c r="G76" s="18" t="n">
         <f aca="false">G75+0*G65</f>
-        <v>22.5362919803019</v>
+        <v>22.536291980302</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56559,11 +56559,11 @@
       </c>
       <c r="F80" s="18" t="n">
         <f aca="false">(F77+F79)*nir_f</f>
-        <v>90.7331490549763</v>
+        <v>90.7331490549764</v>
       </c>
       <c r="G80" s="18" t="n">
         <f aca="false">(G77+G79)*nir_f</f>
-        <v>87.8980128677163</v>
+        <v>87.8980128677164</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56667,11 +56667,11 @@
       </c>
       <c r="F84" s="13" t="n">
         <f aca="false">F83/E83-1</f>
-        <v>0.208277313664672</v>
+        <v>0.208277313664673</v>
       </c>
       <c r="G84" s="13" t="n">
         <f aca="false">G83/F83-1</f>
-        <v>-0.0312469722123508</v>
+        <v>-0.031246972212351</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56719,7 +56719,7 @@
       </c>
       <c r="D90" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E90" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -56887,7 +56887,7 @@
       </c>
       <c r="D97" s="19" t="n">
         <f aca="false">D92*D96/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E97" s="19" t="n">
         <f aca="false">E92*E96/1000</f>
@@ -57026,7 +57026,7 @@
       </c>
       <c r="E103" s="18" t="n">
         <f aca="false">E98*E102*E99</f>
-        <v>389.611657350136</v>
+        <v>389.611657350137</v>
       </c>
       <c r="F103" s="18" t="n">
         <f aca="false">F98*F102*F99</f>
@@ -57034,7 +57034,7 @@
       </c>
       <c r="G103" s="18" t="n">
         <f aca="false">G98*G102*G99</f>
-        <v>601.603748346386</v>
+        <v>601.603748346387</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57755,7 +57755,7 @@
       </c>
       <c r="D137" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E137" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -57923,7 +57923,7 @@
       </c>
       <c r="D144" s="19" t="n">
         <f aca="false">D139*D143/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E144" s="19" t="n">
         <f aca="false">E139*E143/1000</f>
@@ -58062,15 +58062,15 @@
       </c>
       <c r="E150" s="18" t="n">
         <f aca="false">E145*E149*E146</f>
-        <v>286.393643649167</v>
+        <v>286.393643649168</v>
       </c>
       <c r="F150" s="18" t="n">
         <f aca="false">F145*F149*F146</f>
-        <v>374.594055292364</v>
+        <v>374.594055292365</v>
       </c>
       <c r="G150" s="18" t="n">
         <f aca="false">G145*G149*G146</f>
-        <v>409.104523410928</v>
+        <v>409.104523410929</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58214,11 +58214,11 @@
       </c>
       <c r="F157" s="18" t="n">
         <f aca="false">MIN(F150,F155-F156)</f>
-        <v>374.594055292364</v>
+        <v>374.594055292365</v>
       </c>
       <c r="G157" s="18" t="n">
         <f aca="false">MIN(G150,G155-G156)</f>
-        <v>409.104523410928</v>
+        <v>409.104523410929</v>
       </c>
       <c r="H157" s="3" t="s">
         <v>492</v>
@@ -58262,11 +58262,11 @@
       </c>
       <c r="F159" s="18" t="n">
         <f aca="false">F157+F156</f>
-        <v>472.351408181564</v>
+        <v>472.351408181565</v>
       </c>
       <c r="G159" s="18" t="n">
         <f aca="false">G157+G156</f>
-        <v>511.749743944588</v>
+        <v>511.749743944589</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58286,7 +58286,7 @@
       </c>
       <c r="F160" s="13" t="n">
         <f aca="false">F159/E159-1</f>
-        <v>0.419949878633944</v>
+        <v>0.419949878633946</v>
       </c>
       <c r="G160" s="13" t="n">
         <f aca="false">G159/F159-1</f>
@@ -58314,7 +58314,7 @@
       </c>
       <c r="F161" s="13" t="n">
         <f aca="false">F157/F159</f>
-        <v>0.793041046991811</v>
+        <v>0.793041046991812</v>
       </c>
       <c r="G161" s="13" t="n">
         <f aca="false">G157/G159</f>
@@ -58338,11 +58338,11 @@
       </c>
       <c r="F162" s="13" t="n">
         <f aca="false">(F150+F156)/F155</f>
-        <v>0.984708653698991</v>
+        <v>0.984708653698992</v>
       </c>
       <c r="G162" s="13" t="n">
         <f aca="false">(G150+G156)/G155</f>
-        <v>0.906527438863417</v>
+        <v>0.906527438863418</v>
       </c>
       <c r="H162" s="3" t="s">
         <v>497</v>
@@ -58719,7 +58719,7 @@
       </c>
       <c r="G177" s="19" t="n">
         <f aca="false">G174/G176</f>
-        <v>296.23788348544</v>
+        <v>296.237883485441</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58739,11 +58739,11 @@
       </c>
       <c r="F178" s="13" t="n">
         <f aca="false">F177/E177-1</f>
-        <v>0.403445275855607</v>
+        <v>0.403445275855608</v>
       </c>
       <c r="G178" s="13" t="n">
         <f aca="false">G177/F177-1</f>
-        <v>0.0071186210046239</v>
+        <v>0.00711862100462457</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58791,7 +58791,7 @@
       </c>
       <c r="D184" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E184" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -58959,7 +58959,7 @@
       </c>
       <c r="D191" s="19" t="n">
         <f aca="false">D186*D190/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E191" s="19" t="n">
         <f aca="false">E186*E190/1000</f>
@@ -59098,7 +59098,7 @@
       </c>
       <c r="E197" s="18" t="n">
         <f aca="false">E192*E196*E193</f>
-        <v>335.24047830202</v>
+        <v>335.240478302021</v>
       </c>
       <c r="F197" s="18" t="n">
         <f aca="false">F192*F196*F193</f>
@@ -59827,7 +59827,7 @@
       </c>
       <c r="D231" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E231" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -59995,7 +59995,7 @@
       </c>
       <c r="D238" s="19" t="n">
         <f aca="false">D233*D237/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E238" s="19" t="n">
         <f aca="false">E233*E237/1000</f>
@@ -60134,7 +60134,7 @@
       </c>
       <c r="E244" s="18" t="n">
         <f aca="false">E239*E243*E240</f>
-        <v>274.457387061064</v>
+        <v>274.457387061065</v>
       </c>
       <c r="F244" s="18" t="n">
         <f aca="false">F239*F243*F240</f>
@@ -60358,7 +60358,7 @@
       </c>
       <c r="F254" s="13" t="n">
         <f aca="false">F253/E253-1</f>
-        <v>0.327297846991154</v>
+        <v>0.327297846991156</v>
       </c>
       <c r="G254" s="13" t="n">
         <f aca="false">G253/F253-1</f>
@@ -60390,7 +60390,7 @@
       </c>
       <c r="G255" s="13" t="n">
         <f aca="false">G251/G253</f>
-        <v>0.78786275534048</v>
+        <v>0.787862755340481</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60410,11 +60410,11 @@
       </c>
       <c r="F256" s="13" t="n">
         <f aca="false">(F244+F250)/F249</f>
-        <v>0.920456204570842</v>
+        <v>0.920456204570843</v>
       </c>
       <c r="G256" s="13" t="n">
         <f aca="false">(G244+G250)/G249</f>
-        <v>0.857126906110848</v>
+        <v>0.857126906110849</v>
       </c>
       <c r="H256" s="3" t="s">
         <v>497</v>
@@ -60441,7 +60441,7 @@
       </c>
       <c r="G257" s="17" t="n">
         <f aca="false">G251/fx/G233*1000</f>
-        <v>198.093007957081</v>
+        <v>198.093007957082</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60624,7 +60624,7 @@
       </c>
       <c r="F265" s="18" t="n">
         <f aca="false">F261-F264</f>
-        <v>126.583142010994</v>
+        <v>126.583142010995</v>
       </c>
       <c r="G265" s="18" t="n">
         <f aca="false">G261-G264</f>
@@ -60703,11 +60703,11 @@
       </c>
       <c r="F268" s="18" t="n">
         <f aca="false">(F265+F267)*nir_f</f>
-        <v>97.8540193484657</v>
+        <v>97.8540193484658</v>
       </c>
       <c r="G268" s="18" t="n">
         <f aca="false">(G265+G267)*nir_f</f>
-        <v>99.9068484854011</v>
+        <v>99.9068484854012</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60811,11 +60811,11 @@
       </c>
       <c r="F272" s="13" t="n">
         <f aca="false">F271/E271-1</f>
-        <v>0.303104685124674</v>
+        <v>0.303104685124676</v>
       </c>
       <c r="G272" s="13" t="n">
         <f aca="false">G271/F271-1</f>
-        <v>0.0209784856115625</v>
+        <v>0.0209784856115627</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60863,7 +60863,7 @@
       </c>
       <c r="D278" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E278" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -61031,7 +61031,7 @@
       </c>
       <c r="D285" s="19" t="n">
         <f aca="false">D280*D284/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E285" s="19" t="n">
         <f aca="false">E280*E284/1000</f>
@@ -61178,7 +61178,7 @@
       </c>
       <c r="G291" s="18" t="n">
         <f aca="false">G286*G290*G287</f>
-        <v>544.595864288421</v>
+        <v>544.595864288422</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61899,7 +61899,7 @@
       </c>
       <c r="D325" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E325" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -62067,7 +62067,7 @@
       </c>
       <c r="D332" s="19" t="n">
         <f aca="false">D327*D331/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E332" s="19" t="n">
         <f aca="false">E327*E331/1000</f>
@@ -62210,7 +62210,7 @@
       </c>
       <c r="F338" s="18" t="n">
         <f aca="false">F333*F337*F334</f>
-        <v>374.251870979817</v>
+        <v>374.251870979818</v>
       </c>
       <c r="G338" s="18" t="n">
         <f aca="false">G333*G337*G334</f>
@@ -62478,7 +62478,7 @@
       </c>
       <c r="E350" s="13" t="n">
         <f aca="false">(E338+E344)/E343</f>
-        <v>1.21394846156778</v>
+        <v>1.21394846156779</v>
       </c>
       <c r="F350" s="13" t="n">
         <f aca="false">(F338+F344)/F343</f>
@@ -62935,7 +62935,7 @@
       </c>
       <c r="D372" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E372" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -63103,7 +63103,7 @@
       </c>
       <c r="D379" s="19" t="n">
         <f aca="false">D374*D378/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E379" s="19" t="n">
         <f aca="false">E374*E378/1000</f>
@@ -63446,7 +63446,7 @@
       </c>
       <c r="G394" s="18" t="n">
         <f aca="false">G392+G391</f>
-        <v>600.39412875426</v>
+        <v>600.394128754261</v>
       </c>
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63470,7 +63470,7 @@
       </c>
       <c r="G395" s="13" t="n">
         <f aca="false">G394/F394-1</f>
-        <v>0.156275735263847</v>
+        <v>0.156275735263848</v>
       </c>
     </row>
     <row r="396" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63522,7 +63522,7 @@
       </c>
       <c r="G397" s="13" t="n">
         <f aca="false">(G385+G391)/G390</f>
-        <v>0.98910570099604</v>
+        <v>0.989105700996041</v>
       </c>
       <c r="H397" s="3" t="s">
         <v>497</v>
@@ -63923,7 +63923,7 @@
       </c>
       <c r="G413" s="13" t="n">
         <f aca="false">G412/F412-1</f>
-        <v>0.0854169636395812</v>
+        <v>0.0854169636395827</v>
       </c>
     </row>
     <row r="416" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63971,7 +63971,7 @@
       </c>
       <c r="D419" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E419" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -64139,7 +64139,7 @@
       </c>
       <c r="D426" s="19" t="n">
         <f aca="false">D421*D425/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E426" s="19" t="n">
         <f aca="false">E421*E425/1000</f>
@@ -64278,7 +64278,7 @@
       </c>
       <c r="E432" s="18" t="n">
         <f aca="false">E427*E431*E428</f>
-        <v>306.746491421189</v>
+        <v>306.74649142119</v>
       </c>
       <c r="F432" s="18" t="n">
         <f aca="false">F427*F431*F428</f>
@@ -65007,7 +65007,7 @@
       </c>
       <c r="D466" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E466" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -65175,7 +65175,7 @@
       </c>
       <c r="D473" s="19" t="n">
         <f aca="false">D468*D472/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E473" s="19" t="n">
         <f aca="false">E468*E472/1000</f>
@@ -65314,7 +65314,7 @@
       </c>
       <c r="E479" s="18" t="n">
         <f aca="false">E474*E478*E475</f>
-        <v>306.746491421189</v>
+        <v>306.74649142119</v>
       </c>
       <c r="F479" s="18" t="n">
         <f aca="false">F474*F478*F475</f>
@@ -65518,7 +65518,7 @@
       </c>
       <c r="G488" s="18" t="n">
         <f aca="false">G486+G485</f>
-        <v>565.551705178818</v>
+        <v>565.551705178819</v>
       </c>
     </row>
     <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65542,7 +65542,7 @@
       </c>
       <c r="G489" s="13" t="n">
         <f aca="false">G488/F488-1</f>
-        <v>0.124419388268138</v>
+        <v>0.124419388268139</v>
       </c>
     </row>
     <row r="490" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65594,7 +65594,7 @@
       </c>
       <c r="G491" s="13" t="n">
         <f aca="false">(G479+G485)/G484</f>
-        <v>0.909356741995909</v>
+        <v>0.90935674199591</v>
       </c>
       <c r="H491" s="3" t="s">
         <v>497</v>
@@ -65971,7 +65971,7 @@
       </c>
       <c r="G506" s="19" t="n">
         <f aca="false">G503/G505</f>
-        <v>329.928721260655</v>
+        <v>329.928721260656</v>
       </c>
     </row>
     <row r="507" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65995,7 +65995,7 @@
       </c>
       <c r="G507" s="13" t="n">
         <f aca="false">G506/F506-1</f>
-        <v>0.0475214696625417</v>
+        <v>0.047521469662543</v>
       </c>
     </row>
     <row r="510" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66043,7 +66043,7 @@
       </c>
       <c r="D513" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E513" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -66211,7 +66211,7 @@
       </c>
       <c r="D520" s="19" t="n">
         <f aca="false">D515*D519/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E520" s="19" t="n">
         <f aca="false">E515*E519/1000</f>
@@ -66350,7 +66350,7 @@
       </c>
       <c r="E526" s="18" t="n">
         <f aca="false">E521*E525*E522</f>
-        <v>306.746491421189</v>
+        <v>306.74649142119</v>
       </c>
       <c r="F526" s="18" t="n">
         <f aca="false">F521*F525*F522</f>
@@ -67079,7 +67079,7 @@
       </c>
       <c r="D560" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E560" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -67247,7 +67247,7 @@
       </c>
       <c r="D567" s="19" t="n">
         <f aca="false">D562*D566/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E567" s="19" t="n">
         <f aca="false">E562*E566/1000</f>
@@ -67386,7 +67386,7 @@
       </c>
       <c r="E573" s="18" t="n">
         <f aca="false">E568*E572*E569</f>
-        <v>306.746491421189</v>
+        <v>306.74649142119</v>
       </c>
       <c r="F573" s="18" t="n">
         <f aca="false">F568*F572*F569</f>
@@ -67586,11 +67586,11 @@
       </c>
       <c r="F582" s="18" t="n">
         <f aca="false">F580+F579</f>
-        <v>510.284983401044</v>
+        <v>510.284983401045</v>
       </c>
       <c r="G582" s="18" t="n">
         <f aca="false">G580+G579</f>
-        <v>565.551705178818</v>
+        <v>565.551705178819</v>
       </c>
     </row>
     <row r="583" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67610,7 +67610,7 @@
       </c>
       <c r="F583" s="13" t="n">
         <f aca="false">F582/E582-1</f>
-        <v>0.322399265817369</v>
+        <v>0.32239926581737</v>
       </c>
       <c r="G583" s="13" t="n">
         <f aca="false">G582/F582-1</f>
@@ -67662,11 +67662,11 @@
       </c>
       <c r="F585" s="13" t="n">
         <f aca="false">(F573+F579)/F578</f>
-        <v>0.876061192660279</v>
+        <v>0.87606119266028</v>
       </c>
       <c r="G585" s="13" t="n">
         <f aca="false">(G573+G579)/G578</f>
-        <v>0.812297593628961</v>
+        <v>0.812297593628962</v>
       </c>
       <c r="H585" s="3" t="s">
         <v>497</v>
@@ -67820,7 +67820,7 @@
       </c>
       <c r="F592" s="18" t="n">
         <f aca="false">E592*(1+MAX(0,phi*F583))</f>
-        <v>25.5111405760508</v>
+        <v>25.5111405760509</v>
       </c>
       <c r="G592" s="18" t="n">
         <f aca="false">F592*(1+MAX(0,phi*G583))</f>
@@ -67848,7 +67848,7 @@
       </c>
       <c r="F593" s="18" t="n">
         <f aca="false">F592+0*F582</f>
-        <v>25.5111405760508</v>
+        <v>25.5111405760509</v>
       </c>
       <c r="G593" s="18" t="n">
         <f aca="false">G592+0*G582</f>
@@ -68039,11 +68039,11 @@
       </c>
       <c r="F600" s="19" t="n">
         <f aca="false">F597/F599</f>
-        <v>319.686817405118</v>
+        <v>319.686817405119</v>
       </c>
       <c r="G600" s="19" t="n">
         <f aca="false">G597/G599</f>
-        <v>329.589962516167</v>
+        <v>329.589962516168</v>
       </c>
     </row>
     <row r="601" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68063,11 +68063,11 @@
       </c>
       <c r="F601" s="13" t="n">
         <f aca="false">F600/E600-1</f>
-        <v>0.292114425866527</v>
+        <v>0.292114425866528</v>
       </c>
       <c r="G601" s="13" t="n">
         <f aca="false">G600/F600-1</f>
-        <v>0.0309776461582996</v>
+        <v>0.0309776461582998</v>
       </c>
     </row>
     <row r="604" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68115,7 +68115,7 @@
       </c>
       <c r="D607" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E607" s="19" t="n">
         <f aca="false">itc_27*1*mf_lo</f>
@@ -68283,7 +68283,7 @@
       </c>
       <c r="D614" s="19" t="n">
         <f aca="false">D609*D613/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E614" s="19" t="n">
         <f aca="false">E609*E613/1000</f>
@@ -68426,11 +68426,11 @@
       </c>
       <c r="F620" s="18" t="n">
         <f aca="false">F615*F619*F616</f>
-        <v>330.022104409475</v>
+        <v>330.022104409476</v>
       </c>
       <c r="G620" s="18" t="n">
         <f aca="false">G615*G619*G616</f>
-        <v>370.325187716126</v>
+        <v>370.325187716127</v>
       </c>
     </row>
     <row r="621" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68574,11 +68574,11 @@
       </c>
       <c r="F627" s="18" t="n">
         <f aca="false">MIN(F620,F625-F626)</f>
-        <v>330.022104409475</v>
+        <v>330.022104409476</v>
       </c>
       <c r="G627" s="18" t="n">
         <f aca="false">MIN(G620,G625-G626)</f>
-        <v>370.325187716126</v>
+        <v>370.325187716127</v>
       </c>
       <c r="H627" s="3" t="s">
         <v>492</v>
@@ -68622,11 +68622,11 @@
       </c>
       <c r="F629" s="18" t="n">
         <f aca="false">F627+F626</f>
-        <v>427.779457298675</v>
+        <v>427.779457298676</v>
       </c>
       <c r="G629" s="18" t="n">
         <f aca="false">G627+G626</f>
-        <v>472.970408249786</v>
+        <v>472.970408249787</v>
       </c>
     </row>
     <row r="630" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68646,7 +68646,7 @@
       </c>
       <c r="F630" s="13" t="n">
         <f aca="false">F629/E629-1</f>
-        <v>0.285960786719756</v>
+        <v>0.285960786719757</v>
       </c>
       <c r="G630" s="13" t="n">
         <f aca="false">G629/F629-1</f>
@@ -68698,11 +68698,11 @@
       </c>
       <c r="F632" s="13" t="n">
         <f aca="false">(F620+F626)/F625</f>
-        <v>0.891789727267514</v>
+        <v>0.891789727267515</v>
       </c>
       <c r="G632" s="13" t="n">
         <f aca="false">(G620+G626)/G625</f>
-        <v>0.837832667084421</v>
+        <v>0.837832667084422</v>
       </c>
       <c r="H632" s="3" t="s">
         <v>497</v>
@@ -68800,7 +68800,7 @@
       </c>
       <c r="F637" s="18" t="n">
         <f aca="false">F627*F636+F626*$D$635</f>
-        <v>144.712687903442</v>
+        <v>144.712687903443</v>
       </c>
       <c r="G637" s="18" t="n">
         <f aca="false">G627*G636+G626*$D$635</f>
@@ -68991,11 +68991,11 @@
       </c>
       <c r="F644" s="18" t="n">
         <f aca="false">(F641+F643)*nir_f</f>
-        <v>94.4923061633998</v>
+        <v>94.4923061633999</v>
       </c>
       <c r="G644" s="18" t="n">
         <f aca="false">(G641+G643)*nir_f</f>
-        <v>97.4736284021631</v>
+        <v>97.4736284021632</v>
       </c>
     </row>
     <row r="645" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69099,7 +69099,7 @@
       </c>
       <c r="F648" s="13" t="n">
         <f aca="false">F647/E647-1</f>
-        <v>0.25833734464472</v>
+        <v>0.258337344644721</v>
       </c>
       <c r="G648" s="13" t="n">
         <f aca="false">G647/F647-1</f>
@@ -69151,7 +69151,7 @@
       </c>
       <c r="D654" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E654" s="19" t="n">
         <f aca="false">itc_27*1*mf_hi</f>
@@ -69319,7 +69319,7 @@
       </c>
       <c r="D661" s="19" t="n">
         <f aca="false">D656*D660/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E661" s="19" t="n">
         <f aca="false">E656*E660/1000</f>
@@ -69458,7 +69458,7 @@
       </c>
       <c r="E667" s="18" t="n">
         <f aca="false">E662*E666*E663</f>
-        <v>368.095789705427</v>
+        <v>368.095789705428</v>
       </c>
       <c r="F667" s="18" t="n">
         <f aca="false">F662*F666*F663</f>
@@ -69466,7 +69466,7 @@
       </c>
       <c r="G667" s="18" t="n">
         <f aca="false">G662*G666*G663</f>
-        <v>555.487781574189</v>
+        <v>555.48778157419</v>
       </c>
     </row>
     <row r="668" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69730,7 +69730,7 @@
       </c>
       <c r="E679" s="13" t="n">
         <f aca="false">(E667+E673)/E672</f>
-        <v>1.38378101877553</v>
+        <v>1.38378101877554</v>
       </c>
       <c r="F679" s="13" t="n">
         <f aca="false">(F667+F673)/F672</f>
@@ -69738,7 +69738,7 @@
       </c>
       <c r="G679" s="13" t="n">
         <f aca="false">(G667+G673)/G672</f>
-        <v>1.16583473053368</v>
+        <v>1.16583473053369</v>
       </c>
       <c r="H679" s="3" t="s">
         <v>497</v>
@@ -70187,7 +70187,7 @@
       </c>
       <c r="D701" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E701" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -70355,7 +70355,7 @@
       </c>
       <c r="D708" s="19" t="n">
         <f aca="false">D703*D707/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E708" s="19" t="n">
         <f aca="false">E703*E707/1000</f>
@@ -70494,7 +70494,7 @@
       </c>
       <c r="E714" s="18" t="n">
         <f aca="false">E709*E713*E710</f>
-        <v>306.746491421189</v>
+        <v>306.74649142119</v>
       </c>
       <c r="F714" s="18" t="n">
         <f aca="false">F709*F713*F710</f>
@@ -71223,7 +71223,7 @@
       </c>
       <c r="D748" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E748" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -71391,7 +71391,7 @@
       </c>
       <c r="D755" s="19" t="n">
         <f aca="false">D750*D754/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E755" s="19" t="n">
         <f aca="false">E750*E754/1000</f>
@@ -71530,7 +71530,7 @@
       </c>
       <c r="E761" s="18" t="n">
         <f aca="false">E756*E760*E757</f>
-        <v>306.746491421189</v>
+        <v>306.74649142119</v>
       </c>
       <c r="F761" s="18" t="n">
         <f aca="false">F756*F760*F757</f>
@@ -72259,7 +72259,7 @@
       </c>
       <c r="D795" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E795" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -72427,7 +72427,7 @@
       </c>
       <c r="D802" s="19" t="n">
         <f aca="false">D797*D801/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E802" s="19" t="n">
         <f aca="false">E797*E801/1000</f>
@@ -72566,7 +72566,7 @@
       </c>
       <c r="E808" s="18" t="n">
         <f aca="false">E803*E807*E804</f>
-        <v>306.746491421189</v>
+        <v>306.74649142119</v>
       </c>
       <c r="F808" s="18" t="n">
         <f aca="false">F803*F807*F804</f>
@@ -72770,7 +72770,7 @@
       </c>
       <c r="G817" s="18" t="n">
         <f aca="false">G815+G814</f>
-        <v>548.299001145158</v>
+        <v>548.299001145159</v>
       </c>
     </row>
     <row r="818" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -72794,7 +72794,7 @@
       </c>
       <c r="G818" s="13" t="n">
         <f aca="false">G817/F817-1</f>
-        <v>0.143036226610794</v>
+        <v>0.143036226610795</v>
       </c>
     </row>
     <row r="819" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -72846,7 +72846,7 @@
       </c>
       <c r="G820" s="13" t="n">
         <f aca="false">(G808+G814)/G813</f>
-        <v>0.971271788840035</v>
+        <v>0.971271788840036</v>
       </c>
       <c r="H820" s="3" t="s">
         <v>497</v>
@@ -73060,7 +73060,7 @@
       </c>
       <c r="G829" s="18" t="n">
         <f aca="false">G825-G828</f>
-        <v>148.622850274082</v>
+        <v>148.622850274083</v>
       </c>
     </row>
     <row r="830" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -73223,7 +73223,7 @@
       </c>
       <c r="G835" s="19" t="n">
         <f aca="false">G832/G834</f>
-        <v>320.479346048176</v>
+        <v>320.479346048177</v>
       </c>
     </row>
     <row r="836" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -73247,7 +73247,7 @@
       </c>
       <c r="G836" s="13" t="n">
         <f aca="false">G835/F835-1</f>
-        <v>0.0655711456071126</v>
+        <v>0.065571145607114</v>
       </c>
     </row>
     <row r="839" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -73295,7 +73295,7 @@
       </c>
       <c r="D842" s="19" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E842" s="19" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -73463,7 +73463,7 @@
       </c>
       <c r="D849" s="19" t="n">
         <f aca="false">D844*D848/1000</f>
-        <v>8.18983831472237</v>
+        <v>8.18983831472236</v>
       </c>
       <c r="E849" s="19" t="n">
         <f aca="false">E844*E848/1000</f>
@@ -73602,7 +73602,7 @@
       </c>
       <c r="E855" s="18" t="n">
         <f aca="false">E850*E854*E851</f>
-        <v>306.746491421189</v>
+        <v>306.74649142119</v>
       </c>
       <c r="F855" s="18" t="n">
         <f aca="false">F850*F854*F851</f>
@@ -74328,7 +74328,7 @@
       </c>
       <c r="E888" s="17" t="n">
         <f aca="false">tp_w_dcf*C888+(1-tp_w_dcf)*D888</f>
-        <v>5477.38585591289</v>
+        <v>5477.3858559129</v>
       </c>
       <c r="F888" s="13" t="n">
         <f aca="false">E888/E$888-1</f>
@@ -74356,7 +74356,7 @@
       </c>
       <c r="F889" s="13" t="n">
         <f aca="false">E889/E$888-1</f>
-        <v>-0.0533170690610199</v>
+        <v>-0.0533170690610197</v>
       </c>
     </row>
     <row r="890" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -74368,7 +74368,7 @@
       </c>
       <c r="C890" s="17" t="n">
         <f aca="false">(tp_wA*(Val!B89*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!B90*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!B91*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!B92*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B93*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B94*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*(Val!C89*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!C90*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!C91*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!C92*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C93*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C94*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*(Val!D89*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!D90*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!D91*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!D92*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D93*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D94*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
-        <v>5069.81310782481</v>
+        <v>5069.81310782482</v>
       </c>
       <c r="D890" s="17" t="n">
         <f aca="false">Val!B114</f>
@@ -74380,7 +74380,7 @@
       </c>
       <c r="F890" s="13" t="n">
         <f aca="false">E890/E$888-1</f>
-        <v>0.0746470010445159</v>
+        <v>0.0746470010445162</v>
       </c>
     </row>
     <row r="891" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -74392,7 +74392,7 @@
       </c>
       <c r="C891" s="17" t="n">
         <f aca="false">(tp_wA*(Val!B89*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B90*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B91*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B92*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B93*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B94*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B94*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*(Val!C89*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C90*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C91*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C92*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C93*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C94*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C94*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*(Val!D89*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D90*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D91*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D92*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D93*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D94*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D94*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>4710.89338451627</v>
+        <v>4710.89338451628</v>
       </c>
       <c r="D891" s="17" t="n">
         <f aca="false">Val!B114</f>
@@ -74404,7 +74404,7 @@
       </c>
       <c r="F891" s="13" t="n">
         <f aca="false">E891/E$888-1</f>
-        <v>0.041883221684232</v>
+        <v>0.0418832216842324</v>
       </c>
     </row>
     <row r="892" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -74424,11 +74424,11 @@
       </c>
       <c r="E892" s="17" t="n">
         <f aca="false">tp_w_dcf*C892+(1-tp_w_dcf)*D892</f>
-        <v>5319.10305542525</v>
+        <v>5319.10305542526</v>
       </c>
       <c r="F892" s="13" t="n">
         <f aca="false">E892/E$888-1</f>
-        <v>-0.0288975077986833</v>
+        <v>-0.0288975077986831</v>
       </c>
     </row>
     <row r="893" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/emc/dist/20261025_台光電模型_v0.2.1.xlsx
+++ b/emc/dist/20261025_台光電模型_v0.2.1.xlsx
@@ -7089,26 +7089,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7326,26 +7326,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7447,26 +7447,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7568,26 +7568,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7689,26 +7689,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7810,26 +7810,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
